--- a/MapperUI/MapperUI/Input/VueOne_IEC61499_Mapping.xlsx
+++ b/MapperUI/MapperUI/Input/VueOne_IEC61499_Mapping.xlsx
@@ -9,6 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Five_State_Actuator_CAT" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seven_State_Actuator_CAT" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensor_Bool_CAT" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Process_DD_CAT" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -64,7 +65,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -159,6 +160,30 @@
         <fgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF404040"/>
+        <bgColor rgb="FF404040"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFBDD7EE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -245,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -323,6 +348,33 @@
     <xf numFmtId="0" fontId="4" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6401,4 +6453,1908 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" style="19" min="1" max="1"/>
+    <col width="38" customWidth="1" style="19" min="2" max="2"/>
+    <col width="16" customWidth="1" style="19" min="3" max="3"/>
+    <col width="42" customWidth="1" style="19" min="4" max="4"/>
+    <col width="38" customWidth="1" style="19" min="5" max="5"/>
+    <col width="50" customWidth="1" style="19" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="37" t="inlineStr">
+        <is>
+          <t>VueOne Element</t>
+        </is>
+      </c>
+      <c r="B1" s="37" t="inlineStr">
+        <is>
+          <t>IEC 61499 Element</t>
+        </is>
+      </c>
+      <c r="C1" s="37" t="inlineStr">
+        <is>
+          <t>Mapping Type</t>
+        </is>
+      </c>
+      <c r="D1" s="37" t="inlineStr">
+        <is>
+          <t>Transformation Rule</t>
+        </is>
+      </c>
+      <c r="E1" s="37" t="inlineStr">
+        <is>
+          <t>Notes / Phase</t>
+        </is>
+      </c>
+      <c r="F1" s="37" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="38" t="inlineStr">
+        <is>
+          <t>Component-Level Tags (Process)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="39" t="inlineStr">
+        <is>
+          <t>Component/ComponentID</t>
+        </is>
+      </c>
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C3" s="40" t="inlineStr">
+        <is>
+          <t>DISCARDED</t>
+        </is>
+      </c>
+      <c r="D3" s="39" t="inlineStr">
+        <is>
+          <t>IEC 61499 uses GUID instead</t>
+        </is>
+      </c>
+      <c r="E3" s="39" t="inlineStr">
+        <is>
+          <t>VueOne-specific ID</t>
+        </is>
+      </c>
+      <c r="F3" s="39" t="inlineStr">
+        <is>
+          <t>C-0c804da8...</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="41" t="inlineStr">
+        <is>
+          <t>Component/Name</t>
+        </is>
+      </c>
+      <c r="B4" s="41" t="inlineStr">
+        <is>
+          <t>process_name Parameter on CAT instance</t>
+        </is>
+      </c>
+      <c r="C4" s="42" t="inlineStr">
+        <is>
+          <t>TRANSLATED</t>
+        </is>
+      </c>
+      <c r="D4" s="41" t="inlineStr">
+        <is>
+          <t>Maps to process_name InputVar via Parameter in sysres</t>
+        </is>
+      </c>
+      <c r="E4" s="41" t="inlineStr">
+        <is>
+          <t>Phase 2: Instance creation</t>
+        </is>
+      </c>
+      <c r="F4" s="41" t="inlineStr">
+        <is>
+          <t>Feed_Station → Parameter Name='process_name' Value='Feed_Station'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="39" t="inlineStr">
+        <is>
+          <t>Component/VcID</t>
+        </is>
+      </c>
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="40" t="inlineStr">
+        <is>
+          <t>DISCARDED</t>
+        </is>
+      </c>
+      <c r="D5" s="39" t="inlineStr">
+        <is>
+          <t>Visual Components metadata</t>
+        </is>
+      </c>
+      <c r="E5" s="39" t="inlineStr">
+        <is>
+          <t>Not used in control logic</t>
+        </is>
+      </c>
+      <c r="F5" s="39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="41" t="inlineStr">
+        <is>
+          <t>Component/Description</t>
+        </is>
+      </c>
+      <c r="B6" s="41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="40" t="inlineStr">
+        <is>
+          <t>DISCARDED</t>
+        </is>
+      </c>
+      <c r="D6" s="41" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+      <c r="E6" s="41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="39" t="inlineStr">
+        <is>
+          <t>Component/Library_ID</t>
+        </is>
+      </c>
+      <c r="B7" s="39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>DISCARDED</t>
+        </is>
+      </c>
+      <c r="D7" s="39" t="inlineStr">
+        <is>
+          <t>VueOne library reference</t>
+        </is>
+      </c>
+      <c r="E7" s="39" t="inlineStr">
+        <is>
+          <t>Not used in IEC 61499</t>
+        </is>
+      </c>
+      <c r="F7" s="39" t="inlineStr">
+        <is>
+          <t>C-44841856...</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="41" t="inlineStr">
+        <is>
+          <t>Component/Type</t>
+        </is>
+      </c>
+      <c r="B8" s="41" t="inlineStr">
+        <is>
+          <t>FB Type reference</t>
+        </is>
+      </c>
+      <c r="C8" s="42" t="inlineStr">
+        <is>
+          <t>TRANSLATED</t>
+        </is>
+      </c>
+      <c r="D8" s="41" t="inlineStr">
+        <is>
+          <t>Process → Process_DD_CAT</t>
+        </is>
+      </c>
+      <c r="E8" s="41" t="inlineStr">
+        <is>
+          <t>Determines template type</t>
+        </is>
+      </c>
+      <c r="F8" s="41" t="inlineStr">
+        <is>
+          <t>Process → Type='Process_DD_CAT'</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="38" t="inlineStr">
+        <is>
+          <t>Process State Tags (Step Table Source)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="39" t="inlineStr">
+        <is>
+          <t>State/StateID</t>
+        </is>
+      </c>
+      <c r="B10" s="39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C10" s="40" t="inlineStr">
+        <is>
+          <t>DISCARDED</t>
+        </is>
+      </c>
+      <c r="D10" s="39" t="inlineStr">
+        <is>
+          <t>IEC 61499 uses step index instead</t>
+        </is>
+      </c>
+      <c r="E10" s="39" t="inlineStr">
+        <is>
+          <t>VueOne-specific ID</t>
+        </is>
+      </c>
+      <c r="F10" s="39" t="inlineStr">
+        <is>
+          <t>S-96daa832...</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="41" t="inlineStr">
+        <is>
+          <t>State/Name</t>
+        </is>
+      </c>
+      <c r="B11" s="41" t="inlineStr">
+        <is>
+          <t>Text[] Parameter entry (HMI)</t>
+        </is>
+      </c>
+      <c r="C11" s="42" t="inlineStr">
+        <is>
+          <t>TRANSLATED</t>
+        </is>
+      </c>
+      <c r="D11" s="41" t="inlineStr">
+        <is>
+          <t>Copy state name as HMI step description</t>
+        </is>
+      </c>
+      <c r="E11" s="41" t="inlineStr">
+        <is>
+          <t>Phase 2: Parameter generation</t>
+        </is>
+      </c>
+      <c r="F11" s="41" t="inlineStr">
+        <is>
+          <t>CheckPartInHopper → Text[1]='CheckPartInHopper'</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="39" t="inlineStr">
+        <is>
+          <t>State/State_Number</t>
+        </is>
+      </c>
+      <c r="B12" s="39" t="inlineStr">
+        <is>
+          <t>Step index in StepTable arrays</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D12" s="39" t="inlineStr">
+        <is>
+          <t>Used as ordering reference; Mapper assigns sequential step index</t>
+        </is>
+      </c>
+      <c r="E12" s="39" t="inlineStr">
+        <is>
+          <t>Not direct 1:1; Mapper reindexes from 0</t>
+        </is>
+      </c>
+      <c r="F12" s="39" t="inlineStr">
+        <is>
+          <t>State_Number=1 → step index 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="41" t="inlineStr">
+        <is>
+          <t>State/Initial_State</t>
+        </is>
+      </c>
+      <c r="B13" s="41" t="inlineStr">
+        <is>
+          <t>CurrentStep initial value</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D13" s="41" t="inlineStr">
+        <is>
+          <t>True → this is step 0 (engine starts here)</t>
+        </is>
+      </c>
+      <c r="E13" s="41" t="inlineStr">
+        <is>
+          <t>Only one state should be True</t>
+        </is>
+      </c>
+      <c r="F13" s="41" t="inlineStr">
+        <is>
+          <t>True → CurrentStep := 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="39" t="inlineStr">
+        <is>
+          <t>State/Time</t>
+        </is>
+      </c>
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C14" s="44" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="D14" s="39" t="inlineStr">
+        <is>
+          <t>Candidate for future step timeout</t>
+        </is>
+      </c>
+      <c r="E14" s="39" t="inlineStr">
+        <is>
+          <t>Could map to watchdog timer</t>
+        </is>
+      </c>
+      <c r="F14" s="39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="41" t="inlineStr">
+        <is>
+          <t>State/Speed</t>
+        </is>
+      </c>
+      <c r="B15" s="41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="inlineStr">
+        <is>
+          <t>DISCARDED</t>
+        </is>
+      </c>
+      <c r="D15" s="41" t="inlineStr">
+        <is>
+          <t>Not applicable to process steps</t>
+        </is>
+      </c>
+      <c r="E15" s="41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F15" s="41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="39" t="inlineStr">
+        <is>
+          <t>State/Position</t>
+        </is>
+      </c>
+      <c r="B16" s="39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C16" s="40" t="inlineStr">
+        <is>
+          <t>DISCARDED</t>
+        </is>
+      </c>
+      <c r="D16" s="39" t="inlineStr">
+        <is>
+          <t>Not applicable to process steps</t>
+        </is>
+      </c>
+      <c r="E16" s="39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" s="39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="41" t="inlineStr">
+        <is>
+          <t>State/Operator</t>
+        </is>
+      </c>
+      <c r="B17" s="41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C17" s="40" t="inlineStr">
+        <is>
+          <t>DISCARDED</t>
+        </is>
+      </c>
+      <c r="D17" s="41" t="inlineStr">
+        <is>
+          <t>VueOne simulation feature</t>
+        </is>
+      </c>
+      <c r="E17" s="41" t="inlineStr">
+        <is>
+          <t>Not applicable to IEC 61499</t>
+        </is>
+      </c>
+      <c r="F17" s="41" t="inlineStr">
+        <is>
+          <t>equal</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="39" t="inlineStr">
+        <is>
+          <t>State/Counter</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C18" s="40" t="inlineStr">
+        <is>
+          <t>DISCARDED</t>
+        </is>
+      </c>
+      <c r="D18" s="39" t="inlineStr">
+        <is>
+          <t>VueOne counting feature</t>
+        </is>
+      </c>
+      <c r="E18" s="39" t="inlineStr">
+        <is>
+          <t>Not applicable to IEC 61499</t>
+        </is>
+      </c>
+      <c r="F18" s="39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="41" t="inlineStr">
+        <is>
+          <t>State/EndCounter</t>
+        </is>
+      </c>
+      <c r="B19" s="41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C19" s="40" t="inlineStr">
+        <is>
+          <t>DISCARDED</t>
+        </is>
+      </c>
+      <c r="D19" s="41" t="inlineStr">
+        <is>
+          <t>VueOne simulation feature</t>
+        </is>
+      </c>
+      <c r="E19" s="41" t="inlineStr">
+        <is>
+          <t>Not applicable to IEC 61499</t>
+        </is>
+      </c>
+      <c r="F19" s="41" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t>State/StateColour</t>
+        </is>
+      </c>
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C20" s="40" t="inlineStr">
+        <is>
+          <t>DISCARDED</t>
+        </is>
+      </c>
+      <c r="D20" s="39" t="inlineStr">
+        <is>
+          <t>Visual representation only</t>
+        </is>
+      </c>
+      <c r="E20" s="39" t="inlineStr">
+        <is>
+          <t>Not used in control logic</t>
+        </is>
+      </c>
+      <c r="F20" s="39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="41" t="inlineStr">
+        <is>
+          <t>State/RobotAxes</t>
+        </is>
+      </c>
+      <c r="B21" s="41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>DISCARDED</t>
+        </is>
+      </c>
+      <c r="D21" s="41" t="inlineStr">
+        <is>
+          <t>Robot-specific metadata</t>
+        </is>
+      </c>
+      <c r="E21" s="41" t="inlineStr">
+        <is>
+          <t>Not applicable to process</t>
+        </is>
+      </c>
+      <c r="F21" s="41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="39" t="inlineStr">
+        <is>
+          <t>State/StaticState</t>
+        </is>
+      </c>
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t>StepType[] value</t>
+        </is>
+      </c>
+      <c r="C22" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D22" s="39" t="inlineStr">
+        <is>
+          <t>True → WAIT step (type=0). False → ACT step (type=1). Determines whether this step waits for a condition or commands an actuator.</t>
+        </is>
+      </c>
+      <c r="E22" s="39" t="inlineStr">
+        <is>
+          <t>Key classifier for step table generation</t>
+        </is>
+      </c>
+      <c r="F22" s="39" t="inlineStr">
+        <is>
+          <t>True → StepType[n]=0 (WAIT), False → StepType[n]=1 (ACT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="41" t="inlineStr">
+        <is>
+          <t>State/Interlock_Condition</t>
+        </is>
+      </c>
+      <c r="B23" s="41" t="inlineStr">
+        <is>
+          <t>Future: guard condition</t>
+        </is>
+      </c>
+      <c r="C23" s="44" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="D23" s="41" t="inlineStr">
+        <is>
+          <t>Not mapped in current version. Future: could generate explicit interlock data per step.</t>
+        </is>
+      </c>
+      <c r="E23" s="41" t="inlineStr">
+        <is>
+          <t>Phase 4: Safety interlocks</t>
+        </is>
+      </c>
+      <c r="F23" s="41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="38" t="inlineStr">
+        <is>
+          <t>Transition and Sequence Condition Tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="39" t="inlineStr">
+        <is>
+          <t>Transition/TransitionID</t>
+        </is>
+      </c>
+      <c r="B25" s="39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C25" s="40" t="inlineStr">
+        <is>
+          <t>DISCARDED</t>
+        </is>
+      </c>
+      <c r="D25" s="39" t="inlineStr">
+        <is>
+          <t>VueOne-specific ID</t>
+        </is>
+      </c>
+      <c r="E25" s="39" t="inlineStr">
+        <is>
+          <t>Not used in IEC 61499</t>
+        </is>
+      </c>
+      <c r="F25" s="39" t="inlineStr">
+        <is>
+          <t>T-fa850de7...</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="41" t="inlineStr">
+        <is>
+          <t>Transition/Type</t>
+        </is>
+      </c>
+      <c r="B26" s="41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C26" s="40" t="inlineStr">
+        <is>
+          <t>DISCARDED</t>
+        </is>
+      </c>
+      <c r="D26" s="41" t="inlineStr">
+        <is>
+          <t>Always SINGLE for process states</t>
+        </is>
+      </c>
+      <c r="E26" s="41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F26" s="41" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="39" t="inlineStr">
+        <is>
+          <t>Transition/Origin_State</t>
+        </is>
+      </c>
+      <c r="B27" s="39" t="inlineStr">
+        <is>
+          <t>Current step (implicit)</t>
+        </is>
+      </c>
+      <c r="C27" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D27" s="39" t="inlineStr">
+        <is>
+          <t>The step currently being processed; used to maintain ordering</t>
+        </is>
+      </c>
+      <c r="E27" s="39" t="inlineStr">
+        <is>
+          <t>Mapper walks origin→destination chain</t>
+        </is>
+      </c>
+      <c r="F27" s="39" t="inlineStr">
+        <is>
+          <t>S-96daa832 → step 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="41" t="inlineStr">
+        <is>
+          <t>Transition/Destination_State</t>
+        </is>
+      </c>
+      <c r="B28" s="41" t="inlineStr">
+        <is>
+          <t>NextStep[] value</t>
+        </is>
+      </c>
+      <c r="C28" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D28" s="41" t="inlineStr">
+        <is>
+          <t>Maps to the index of the next step. Mapper resolves StateID to step index.</t>
+        </is>
+      </c>
+      <c r="E28" s="41" t="inlineStr">
+        <is>
+          <t>Phase 2: NextStep array generation</t>
+        </is>
+      </c>
+      <c r="F28" s="41" t="inlineStr">
+        <is>
+          <t>Dest S-fe4fd8c4 → NextStep[0]=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="39" t="inlineStr">
+        <is>
+          <t>Transition/Priority</t>
+        </is>
+      </c>
+      <c r="B29" s="39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C29" s="40" t="inlineStr">
+        <is>
+          <t>DISCARDED</t>
+        </is>
+      </c>
+      <c r="D29" s="39" t="inlineStr">
+        <is>
+          <t>Single transitions only; no priority needed</t>
+        </is>
+      </c>
+      <c r="E29" s="39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F29" s="39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="41" t="inlineStr">
+        <is>
+          <t>Sequence_Condition/ConditionGroup</t>
+        </is>
+      </c>
+      <c r="B30" s="41" t="inlineStr">
+        <is>
+          <t>Wait/Done condition</t>
+        </is>
+      </c>
+      <c r="C30" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D30" s="41" t="inlineStr">
+        <is>
+          <t>Contains one or more Condition elements. Each maps to a Wait1Id + Wait1State pair.</t>
+        </is>
+      </c>
+      <c r="E30" s="41" t="inlineStr">
+        <is>
+          <t>Compound conditions need future extension</t>
+        </is>
+      </c>
+      <c r="F30" s="41" t="inlineStr">
+        <is>
+          <t>Group_1 with Operator=''</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="39" t="inlineStr">
+        <is>
+          <t>Condition/@ID</t>
+        </is>
+      </c>
+      <c r="B31" s="39" t="inlineStr">
+        <is>
+          <t>Wait1State[] value</t>
+        </is>
+      </c>
+      <c r="C31" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D31" s="39" t="inlineStr">
+        <is>
+          <t>The StateID references a specific state of the target component. Mapper resolves to numeric state value.</t>
+        </is>
+      </c>
+      <c r="E31" s="39" t="inlineStr">
+        <is>
+          <t>Cross-reference with target component states</t>
+        </is>
+      </c>
+      <c r="F31" s="39" t="inlineStr">
+        <is>
+          <t>S-64af871a (On) → Wait1State[n]=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="41" t="inlineStr">
+        <is>
+          <t>Condition/@Name</t>
+        </is>
+      </c>
+      <c r="B32" s="41" t="inlineStr">
+        <is>
+          <t>Component/State name lookup</t>
+        </is>
+      </c>
+      <c r="C32" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D32" s="41" t="inlineStr">
+        <is>
+          <t>Format: "ComponentName/StateName". Mapper splits on "/" to identify which component and which state.</t>
+        </is>
+      </c>
+      <c r="E32" s="41" t="inlineStr">
+        <is>
+          <t>Key field for resolving wait conditions</t>
+        </is>
+      </c>
+      <c r="F32" s="41" t="inlineStr">
+        <is>
+          <t>'PartInHopper/On' → comp=PartInHopper, state=On</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="39" t="inlineStr">
+        <is>
+          <t>Condition/@ComponentID</t>
+        </is>
+      </c>
+      <c r="B33" s="39" t="inlineStr">
+        <is>
+          <t>Wait1Id[] value</t>
+        </is>
+      </c>
+      <c r="C33" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D33" s="39" t="inlineStr">
+        <is>
+          <t>Identifies the component being referenced. Mapper assigns sequential comp_id and uses it as Wait1Id.</t>
+        </is>
+      </c>
+      <c r="E33" s="39" t="inlineStr">
+        <is>
+          <t>Cross-reference with Component Registry</t>
+        </is>
+      </c>
+      <c r="F33" s="39" t="inlineStr">
+        <is>
+          <t>C-eaa52671 (PartInHopper) → Wait1Id[n]=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="38" t="inlineStr">
+        <is>
+          <t>Step Table Array Generation (Mapper Output)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="39" t="inlineStr">
+        <is>
+          <t>Process states (ordered walk)</t>
+        </is>
+      </c>
+      <c r="B35" s="39" t="inlineStr">
+        <is>
+          <t>StepType[] Parameter</t>
+        </is>
+      </c>
+      <c r="C35" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D35" s="39" t="inlineStr">
+        <is>
+          <t>Mapper walks states in order. StaticState=True → type 0 (WAIT). StaticState=False → type 1 (ACT). Last step → type 9 (END).</t>
+        </is>
+      </c>
+      <c r="E35" s="39" t="inlineStr">
+        <is>
+          <t>Phase 2: Array generation</t>
+        </is>
+      </c>
+      <c r="F35" s="39" t="inlineStr">
+        <is>
+          <t>Value='[0,1,0,1,1,1]'</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="41" t="inlineStr">
+        <is>
+          <t>ACT state + referenced component</t>
+        </is>
+      </c>
+      <c r="B36" s="41" t="inlineStr">
+        <is>
+          <t>CmdTargetName[] Parameter</t>
+        </is>
+      </c>
+      <c r="C36" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D36" s="41" t="inlineStr">
+        <is>
+          <t>For ACT steps, extract the actuator name from the Condition/@Name field (part before "/"). For WAIT steps, empty string.</t>
+        </is>
+      </c>
+      <c r="E36" s="41" t="inlineStr">
+        <is>
+          <t>Phase 2: Array generation</t>
+        </is>
+      </c>
+      <c r="F36" s="41" t="inlineStr">
+        <is>
+          <t>Value='[\'\',\'Pusher\',\'\',\'Checker\',\'Checker\',\'Pusher\']'</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="39" t="inlineStr">
+        <is>
+          <t>ACT state + referenced state value</t>
+        </is>
+      </c>
+      <c r="B37" s="39" t="inlineStr">
+        <is>
+          <t>CmdStateArr[] Parameter</t>
+        </is>
+      </c>
+      <c r="C37" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D37" s="39" t="inlineStr">
+        <is>
+          <t>For ACT steps, the dynamic state number of the target actuator (1=GO_WORK, 3=GO_HOME). Mapper infers from state name (Advancing→1, Returning→3).</t>
+        </is>
+      </c>
+      <c r="E37" s="39" t="inlineStr">
+        <is>
+          <t>Phase 2: Array generation</t>
+        </is>
+      </c>
+      <c r="F37" s="39" t="inlineStr">
+        <is>
+          <t>Value='[0,1,0,1,3,3]'</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="41" t="inlineStr">
+        <is>
+          <t>Condition/@ComponentID resolution</t>
+        </is>
+      </c>
+      <c r="B38" s="41" t="inlineStr">
+        <is>
+          <t>Wait1Id[] Parameter</t>
+        </is>
+      </c>
+      <c r="C38" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D38" s="41" t="inlineStr">
+        <is>
+          <t>Mapper assigns sequential comp_id per component in station. The Condition/@ComponentID resolves to this numeric ID.</t>
+        </is>
+      </c>
+      <c r="E38" s="41" t="inlineStr">
+        <is>
+          <t>Phase 2: Array generation</t>
+        </is>
+      </c>
+      <c r="F38" s="41" t="inlineStr">
+        <is>
+          <t>Value='[3,0,4,1,1,0]'</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="39" t="inlineStr">
+        <is>
+          <t>Condition/@ID state resolution</t>
+        </is>
+      </c>
+      <c r="B39" s="39" t="inlineStr">
+        <is>
+          <t>Wait1State[] Parameter</t>
+        </is>
+      </c>
+      <c r="C39" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D39" s="39" t="inlineStr">
+        <is>
+          <t>The referenced state number from the target component. E.g. Feeder/Advanced → State_Number 2 → AT_WORK.</t>
+        </is>
+      </c>
+      <c r="E39" s="39" t="inlineStr">
+        <is>
+          <t>Phase 2: Array generation</t>
+        </is>
+      </c>
+      <c r="F39" s="39" t="inlineStr">
+        <is>
+          <t>Value='[1,2,1,2,4,4]'</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="41" t="inlineStr">
+        <is>
+          <t>Transition chain</t>
+        </is>
+      </c>
+      <c r="B40" s="41" t="inlineStr">
+        <is>
+          <t>NextStep[] Parameter</t>
+        </is>
+      </c>
+      <c r="C40" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D40" s="41" t="inlineStr">
+        <is>
+          <t>Destination_State resolved to step index. Last step loops to 0.</t>
+        </is>
+      </c>
+      <c r="E40" s="41" t="inlineStr">
+        <is>
+          <t>Phase 2: Array generation</t>
+        </is>
+      </c>
+      <c r="F40" s="41" t="inlineStr">
+        <is>
+          <t>Value='[1,2,3,4,5,0]'</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="39" t="inlineStr">
+        <is>
+          <t>State/Name sequence</t>
+        </is>
+      </c>
+      <c r="B41" s="39" t="inlineStr">
+        <is>
+          <t>Text[] Parameter</t>
+        </is>
+      </c>
+      <c r="C41" s="42" t="inlineStr">
+        <is>
+          <t>TRANSLATED</t>
+        </is>
+      </c>
+      <c r="D41" s="39" t="inlineStr">
+        <is>
+          <t>Human-readable step descriptions for HMI faceplate.</t>
+        </is>
+      </c>
+      <c r="E41" s="39" t="inlineStr">
+        <is>
+          <t>Phase 2: Array generation</t>
+        </is>
+      </c>
+      <c r="F41" s="39" t="inlineStr">
+        <is>
+          <t>Value='[\'CheckPartInHopper\',\'FeederAdvancing\',...]'</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="38" t="inlineStr">
+        <is>
+          <t>Component Registry Generation (Mapper Output)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="39" t="inlineStr">
+        <is>
+          <t>All components in process scope</t>
+        </is>
+      </c>
+      <c r="B43" s="39" t="inlineStr">
+        <is>
+          <t>cr_name[] Parameter</t>
+        </is>
+      </c>
+      <c r="C43" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D43" s="39" t="inlineStr">
+        <is>
+          <t>Mapper assigns sequential ID (0,1,2...) to each component referenced by this process. Array maps ID to name.</t>
+        </is>
+      </c>
+      <c r="E43" s="39" t="inlineStr">
+        <is>
+          <t>Phase 2: Used by engine for command dest_name</t>
+        </is>
+      </c>
+      <c r="F43" s="39" t="inlineStr">
+        <is>
+          <t>Value='[\'Pusher\',\'Checker\',\'Transfer\',\'HopperSensor\',\'PartAtChecker\']'</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="41" t="inlineStr">
+        <is>
+          <t>Component count</t>
+        </is>
+      </c>
+      <c r="B44" s="41" t="inlineStr">
+        <is>
+          <t>num_comps Parameter</t>
+        </is>
+      </c>
+      <c r="C44" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D44" s="41" t="inlineStr">
+        <is>
+          <t>Total number of unique components in the registry.</t>
+        </is>
+      </c>
+      <c r="E44" s="41" t="inlineStr">
+        <is>
+          <t>Phase 2: Engine config</t>
+        </is>
+      </c>
+      <c r="F44" s="41" t="inlineStr">
+        <is>
+          <t>Value='5'</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="39" t="inlineStr">
+        <is>
+          <t>Step count</t>
+        </is>
+      </c>
+      <c r="B45" s="39" t="inlineStr">
+        <is>
+          <t>num_steps Parameter</t>
+        </is>
+      </c>
+      <c r="C45" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D45" s="39" t="inlineStr">
+        <is>
+          <t>Total number of steps in the StepTable.</t>
+        </is>
+      </c>
+      <c r="E45" s="39" t="inlineStr">
+        <is>
+          <t>Phase 2: Engine config</t>
+        </is>
+      </c>
+      <c r="F45" s="39" t="inlineStr">
+        <is>
+          <t>Value='6'</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="38" t="inlineStr">
+        <is>
+          <t>CAT Instance Injection (sysres File)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="39" t="inlineStr">
+        <is>
+          <t>Process component</t>
+        </is>
+      </c>
+      <c r="B47" s="39" t="inlineStr">
+        <is>
+          <t>&lt;FB&gt; element in sysres</t>
+        </is>
+      </c>
+      <c r="C47" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D47" s="39" t="inlineStr">
+        <is>
+          <t>Mapper creates &lt;FB Name='Process1' Type='Process_DD_CAT' Namespace='Main'&gt; with child Parameter elements for all arrays.</t>
+        </is>
+      </c>
+      <c r="E47" s="39" t="inlineStr">
+        <is>
+          <t>Phase 3: Instance injection</t>
+        </is>
+      </c>
+      <c r="F47" s="39" t="inlineStr">
+        <is>
+          <t>&lt;FB Name='Feed_Station' Type='Process_DD_CAT'&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="41" t="inlineStr">
+        <is>
+          <t>process_name</t>
+        </is>
+      </c>
+      <c r="B48" s="41" t="inlineStr">
+        <is>
+          <t>Parameter Name='process_name'</t>
+        </is>
+      </c>
+      <c r="C48" s="42" t="inlineStr">
+        <is>
+          <t>TRANSLATED</t>
+        </is>
+      </c>
+      <c r="D48" s="41" t="inlineStr">
+        <is>
+          <t>Direct copy of Component/Name as string Parameter.</t>
+        </is>
+      </c>
+      <c r="E48" s="41" t="inlineStr">
+        <is>
+          <t>Phase 3: sysres</t>
+        </is>
+      </c>
+      <c r="F48" s="41" t="inlineStr">
+        <is>
+          <t>Value='\'Feed_Station\''</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="39" t="inlineStr">
+        <is>
+          <t>process_id</t>
+        </is>
+      </c>
+      <c r="B49" s="39" t="inlineStr">
+        <is>
+          <t>Parameter Name='process_id'</t>
+        </is>
+      </c>
+      <c r="C49" s="44" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="D49" s="39" t="inlineStr">
+        <is>
+          <t>Mapper assigns unique ID within station scope. Must not collide with actuator/sensor IDs in state_table.</t>
+        </is>
+      </c>
+      <c r="E49" s="39" t="inlineStr">
+        <is>
+          <t>Phase 3: sysres</t>
+        </is>
+      </c>
+      <c r="F49" s="39" t="inlineStr">
+        <is>
+          <t>Value='10'</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="41" t="inlineStr">
+        <is>
+          <t>StepType[]</t>
+        </is>
+      </c>
+      <c r="B50" s="41" t="inlineStr">
+        <is>
+          <t>Parameter Name='st_type'</t>
+        </is>
+      </c>
+      <c r="C50" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D50" s="41" t="inlineStr">
+        <is>
+          <t>Square bracket array syntax in Parameter Value attribute.</t>
+        </is>
+      </c>
+      <c r="E50" s="41" t="inlineStr">
+        <is>
+          <t>Phase 3: sysres</t>
+        </is>
+      </c>
+      <c r="F50" s="41" t="inlineStr">
+        <is>
+          <t>Value='[0,1,0,1,1,1]'</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="39" t="inlineStr">
+        <is>
+          <t>CmdTargetName[]</t>
+        </is>
+      </c>
+      <c r="B51" s="39" t="inlineStr">
+        <is>
+          <t>Parameter Name='cmd_target'</t>
+        </is>
+      </c>
+      <c r="C51" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D51" s="39" t="inlineStr">
+        <is>
+          <t>String array with component names per step.</t>
+        </is>
+      </c>
+      <c r="E51" s="39" t="inlineStr">
+        <is>
+          <t>Phase 3: sysres</t>
+        </is>
+      </c>
+      <c r="F51" s="39" t="inlineStr">
+        <is>
+          <t>Value='[\'Pusher\',...]'</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="41" t="inlineStr">
+        <is>
+          <t>CmdStateArr[]</t>
+        </is>
+      </c>
+      <c r="B52" s="41" t="inlineStr">
+        <is>
+          <t>Parameter Name='cmd_state'</t>
+        </is>
+      </c>
+      <c r="C52" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D52" s="41" t="inlineStr">
+        <is>
+          <t>INT array with commanded state values per step.</t>
+        </is>
+      </c>
+      <c r="E52" s="41" t="inlineStr">
+        <is>
+          <t>Phase 3: sysres</t>
+        </is>
+      </c>
+      <c r="F52" s="41" t="inlineStr">
+        <is>
+          <t>Value='[0,1,0,1,3,3]'</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="39" t="inlineStr">
+        <is>
+          <t>Wait1Id[]</t>
+        </is>
+      </c>
+      <c r="B53" s="39" t="inlineStr">
+        <is>
+          <t>Parameter Name='st_wait_comp'</t>
+        </is>
+      </c>
+      <c r="C53" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D53" s="39" t="inlineStr">
+        <is>
+          <t>INT array with component IDs to monitor per step.</t>
+        </is>
+      </c>
+      <c r="E53" s="39" t="inlineStr">
+        <is>
+          <t>Phase 3: sysres</t>
+        </is>
+      </c>
+      <c r="F53" s="39" t="inlineStr">
+        <is>
+          <t>Value='[3,0,4,1,1,0]'</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="41" t="inlineStr">
+        <is>
+          <t>Wait1State[]</t>
+        </is>
+      </c>
+      <c r="B54" s="41" t="inlineStr">
+        <is>
+          <t>Parameter Name='st_wait_state'</t>
+        </is>
+      </c>
+      <c r="C54" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D54" s="41" t="inlineStr">
+        <is>
+          <t>INT array with target state values per step.</t>
+        </is>
+      </c>
+      <c r="E54" s="41" t="inlineStr">
+        <is>
+          <t>Phase 3: sysres</t>
+        </is>
+      </c>
+      <c r="F54" s="41" t="inlineStr">
+        <is>
+          <t>Value='[1,2,1,2,4,4]'</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="39" t="inlineStr">
+        <is>
+          <t>NextStep[]</t>
+        </is>
+      </c>
+      <c r="B55" s="39" t="inlineStr">
+        <is>
+          <t>Parameter Name='st_next'</t>
+        </is>
+      </c>
+      <c r="C55" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D55" s="39" t="inlineStr">
+        <is>
+          <t>INT array with next step index per step.</t>
+        </is>
+      </c>
+      <c r="E55" s="39" t="inlineStr">
+        <is>
+          <t>Phase 3: sysres</t>
+        </is>
+      </c>
+      <c r="F55" s="39" t="inlineStr">
+        <is>
+          <t>Value='[1,2,3,4,5,0]'</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="41" t="inlineStr">
+        <is>
+          <t>Text[]</t>
+        </is>
+      </c>
+      <c r="B56" s="41" t="inlineStr">
+        <is>
+          <t>Parameter Name='Text'</t>
+        </is>
+      </c>
+      <c r="C56" s="42" t="inlineStr">
+        <is>
+          <t>TRANSLATED</t>
+        </is>
+      </c>
+      <c r="D56" s="41" t="inlineStr">
+        <is>
+          <t>String array with HMI step descriptions.</t>
+        </is>
+      </c>
+      <c r="E56" s="41" t="inlineStr">
+        <is>
+          <t>Phase 3: sysres</t>
+        </is>
+      </c>
+      <c r="F56" s="41" t="inlineStr">
+        <is>
+          <t>Value='[\'CheckPartInHopper\',...]'</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="39" t="inlineStr">
+        <is>
+          <t>cr_name[]</t>
+        </is>
+      </c>
+      <c r="B57" s="39" t="inlineStr">
+        <is>
+          <t>Parameter Name='cr_name'</t>
+        </is>
+      </c>
+      <c r="C57" s="43" t="inlineStr">
+        <is>
+          <t>ENCODED</t>
+        </is>
+      </c>
+      <c r="D57" s="39" t="inlineStr">
+        <is>
+          <t>String array mapping comp_id to name.</t>
+        </is>
+      </c>
+      <c r="E57" s="39" t="inlineStr">
+        <is>
+          <t>Phase 3: sysres</t>
+        </is>
+      </c>
+      <c r="F57" s="39" t="inlineStr">
+        <is>
+          <t>Value='[\'Pusher\',\'Checker\',...]'</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="38" t="inlineStr">
+        <is>
+          <t>IEC 61499 Template: Process_DD_CAT (HARDCODED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B59" s="39" t="inlineStr">
+        <is>
+          <t>FBType Name='Process_DD_CAT'</t>
+        </is>
+      </c>
+      <c r="C59" s="45" t="inlineStr">
+        <is>
+          <t>HARDCODED</t>
+        </is>
+      </c>
+      <c r="D59" s="39" t="inlineStr">
+        <is>
+          <t>CAT composite FB type, pre-validated</t>
+        </is>
+      </c>
+      <c r="E59" s="39" t="inlineStr">
+        <is>
+          <t>GUID generated fresh per project</t>
+        </is>
+      </c>
+      <c r="F59" s="39" t="inlineStr">
+        <is>
+          <t>Name='Process_DD_CAT' Namespace='Main'</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B60" s="41" t="inlineStr">
+        <is>
+          <t>ProcessRuntime_Generic_v1 (BFB)</t>
+        </is>
+      </c>
+      <c r="C60" s="45" t="inlineStr">
+        <is>
+          <t>HARDCODED</t>
+        </is>
+      </c>
+      <c r="D60" s="41" t="inlineStr">
+        <is>
+          <t>Generic step executor inside CAT. Fixed ECC, fixed algorithms. Reads InputVar arrays.</t>
+        </is>
+      </c>
+      <c r="E60" s="41" t="inlineStr">
+        <is>
+          <t>Never modified by Mapper</t>
+        </is>
+      </c>
+      <c r="F60" s="41" t="inlineStr">
+        <is>
+          <t>ECC: START→INIT→IDLE→CMD/WAIT→ADVANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B61" s="39" t="inlineStr">
+        <is>
+          <t>ProcessStateBusHandler (BFB)</t>
+        </is>
+      </c>
+      <c r="C61" s="45" t="inlineStr">
+        <is>
+          <t>HARDCODED</t>
+        </is>
+      </c>
+      <c r="D61" s="39" t="inlineStr">
+        <is>
+          <t>Ring communication layer inside CAT. Receives state reports, publishes commands.</t>
+        </is>
+      </c>
+      <c r="E61" s="39" t="inlineStr">
+        <is>
+          <t>Never modified by Mapper</t>
+        </is>
+      </c>
+      <c r="F61" s="39" t="inlineStr">
+        <is>
+          <t>BREQ→update state_table, CMDREQ→publish command</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B62" s="41" t="inlineStr">
+        <is>
+          <t>stateRptCmdAdptr (socket + plug)</t>
+        </is>
+      </c>
+      <c r="C62" s="45" t="inlineStr">
+        <is>
+          <t>HARDCODED</t>
+        </is>
+      </c>
+      <c r="D62" s="41" t="inlineStr">
+        <is>
+          <t>Adapter pair connecting CAT to the station state/command ring.</t>
+        </is>
+      </c>
+      <c r="E62" s="41" t="inlineStr">
+        <is>
+          <t>Wired in station system file</t>
+        </is>
+      </c>
+      <c r="F62" s="41" t="inlineStr">
+        <is>
+          <t>stateRprtCmd_in / stateRprtCmd_out</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B63" s="39" t="inlineStr">
+        <is>
+          <t>CaSAdptr (socket + plug)</t>
+        </is>
+      </c>
+      <c r="C63" s="45" t="inlineStr">
+        <is>
+          <t>HARDCODED</t>
+        </is>
+      </c>
+      <c r="D63" s="39" t="inlineStr">
+        <is>
+          <t>Adapter pair for mode and cycle type chain from station.</t>
+        </is>
+      </c>
+      <c r="E63" s="39" t="inlineStr">
+        <is>
+          <t>Wired in station system file</t>
+        </is>
+      </c>
+      <c r="F63" s="39" t="inlineStr">
+        <is>
+          <t>stationAdptr_in / stationAdptr_out</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B64" s="41" t="inlineStr">
+        <is>
+          <t>Process_DD_CAT_HMI (SIFB)</t>
+        </is>
+      </c>
+      <c r="C64" s="45" t="inlineStr">
+        <is>
+          <t>HARDCODED</t>
+        </is>
+      </c>
+      <c r="D64" s="41" t="inlineStr">
+        <is>
+          <t>HMI Service Interface FB (iThis). Exposes step text, engine state.</t>
+        </is>
+      </c>
+      <c r="E64" s="41" t="inlineStr">
+        <is>
+          <t>EAE auto-generates faceplate</t>
+        </is>
+      </c>
+      <c r="F64" s="41" t="inlineStr">
+        <is>
+          <t>current_step, ThisStepText, engine_state</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A34:F34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>